--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98264</v>
+        <v>98272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98274</v>
+        <v>98282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>98287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,314 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128366414</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>730206</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7119744</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128366412</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91355</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>730248</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7119759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128366420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730220</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7119761</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>91355</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>91452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91452</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>91467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>91494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -987,7 +987,7 @@
         <v>128366420</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,42 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R4" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128366412</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366414</v>
+        <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730206</v>
+        <v>730248</v>
       </c>
       <c r="R3" t="n">
-        <v>7119744</v>
+        <v>7119759</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366412</v>
+        <v>128366414</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730248</v>
+        <v>730206</v>
       </c>
       <c r="R4" t="n">
-        <v>7119759</v>
+        <v>7119744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128366412</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99012</v>
+        <v>99015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99015</v>
+        <v>99023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99023</v>
+        <v>99033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99036</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742752</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742752</v>
+        <v>128366412</v>
       </c>
       <c r="B2" t="n">
-        <v>99043</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finn-Olles- NV, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730240</v>
+        <v>730248</v>
       </c>
       <c r="R2" t="n">
-        <v>7119961</v>
+        <v>7119759</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,33 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366412</v>
+        <v>128384243</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730248</v>
+        <v>730253</v>
       </c>
       <c r="R3" t="n">
-        <v>7119759</v>
+        <v>7119755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,62 +857,54 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366414</v>
+        <v>128384260</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730206</v>
+        <v>730242</v>
       </c>
       <c r="R4" t="n">
         <v>7119744</v>
@@ -967,39 +954,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128366420</v>
+        <v>128366414</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1010,7 +997,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1018,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730220</v>
+        <v>730206</v>
       </c>
       <c r="R5" t="n">
-        <v>7119761</v>
+        <v>7119744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,11 +1047,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1082,6 +1068,922 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128366417</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730258</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7119760</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128366420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730220</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7119761</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122742752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finn-Olles- NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730240</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7119961</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122743077</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rengärde S, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730248</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7119841</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122743079</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rengärde SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730266</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7119901</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122743080</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rengärde SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730256</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7119895</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122743081</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rengärde SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730239</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7119874</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122743090</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nedre Rosinedal SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730210</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7119844</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122743091</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nedre Rosinedal SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>730197</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7119830</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28706-2024 artfynd.xlsx
+++ b/artfynd/A 28706-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384243</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384260</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366417</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366420</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742752</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743079</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743080</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743081</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1984,8 +2049,28 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>